--- a/artfynd/A 13462-2022 artfynd.xlsx
+++ b/artfynd/A 13462-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6820,6 +6820,118 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>102716810</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>V Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>567964</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7191945</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13462-2022 artfynd.xlsx
+++ b/artfynd/A 13462-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
